--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -723,7 +723,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -759,9 +759,26 @@
         <v>dev</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>khaled</v>
+      </c>
+      <c r="B3" t="str">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>200</v>
+      </c>
+      <c r="D3">
+        <v>6000</v>
+      </c>
+      <c r="E3" t="str">
+        <v>dev</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -997,10 +1014,39 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:D2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>collaborateur</v>
+      </c>
+      <c r="B1" t="str">
+        <v>contact</v>
+      </c>
+      <c r="C1" t="str">
+        <v>description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>montant</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SAIDANA</v>
+      </c>
+      <c r="B2" t="str">
+        <v xml:space="preserve">mansour 53.185.773 </v>
+      </c>
+      <c r="C2" t="str">
+        <v xml:space="preserve">câblage des armoire électriques </v>
+      </c>
+      <c r="D2">
+        <v>7141</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/projets/Projet_sonede_redondance.xlsx
+++ b/src/assets/projets/Projet_sonede_redondance.xlsx
@@ -495,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -684,19 +684,65 @@
         <v>95942</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LA PLANET ELECTRIQUE</v>
+      </c>
+      <c r="B12" t="str">
+        <v>CABLE TRANS DONNEE BLINDE 1500</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>8466.255</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:D2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>fournisseur</v>
+      </c>
+      <c r="B1" t="str">
+        <v>description</v>
+      </c>
+      <c r="C1" t="str">
+        <v>montant</v>
+      </c>
+      <c r="D1" t="str">
+        <v>date</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>habachi</v>
+      </c>
+      <c r="B2" t="str">
+        <v>matériel électrique sans facture</v>
+      </c>
+      <c r="C2">
+        <v>200</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-08-10</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -785,10 +831,261 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:G14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>fournisseur</v>
+      </c>
+      <c r="B1" t="str">
+        <v>date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>etat</v>
+      </c>
+      <c r="D1" t="str">
+        <v>montant</v>
+      </c>
+      <c r="E1" t="str">
+        <v>id</v>
+      </c>
+      <c r="F1" t="str">
+        <v>nom</v>
+      </c>
+      <c r="G1" t="str">
+        <v>retenuSource</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>MASTER MOTION</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C2" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D2">
+        <v>4943.758</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>MASTER MOTION</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D3">
+        <v>51753.304</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MASTER MOTION</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="C4" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D4">
+        <v>38721.17</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PAY-1789054573814-1</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4">
+        <v>391.12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>MASTER MOTION</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D5">
+        <v>38721.17</v>
+      </c>
+      <c r="E5" t="str">
+        <v>PAY-1789054573814-2</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5">
+        <v>391.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AMEL</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C6" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D6">
+        <v>5988.004</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>EGAS</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-24</v>
+      </c>
+      <c r="C7" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D7">
+        <v>1568.287</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AMF</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D8">
+        <v>3798.48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>H2M</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="D9">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AVEVA</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="C10" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D10">
+        <v>95942</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SAIDANA</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C11" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D11">
+        <v>7141</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LA PLANET ELECTRIQUE</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="C12" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D12">
+        <v>3352.64</v>
+      </c>
+      <c r="E12" t="str">
+        <v>PAY-1789134017086-1</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12">
+        <v>33.87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LA PLANET ELECTRIQUE</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="C13" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D13">
+        <v>2514.48</v>
+      </c>
+      <c r="E13" t="str">
+        <v>PAY-1789134017086-2</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LA PLANET ELECTRIQUE</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-11-12</v>
+      </c>
+      <c r="C14" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="D14">
+        <v>2514.48</v>
+      </c>
+      <c r="E14" t="str">
+        <v>PAY-1789134017086-3</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14">
+        <v>25.4</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1014,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1044,9 +1341,23 @@
         <v>7141</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SAIDANA</v>
+      </c>
+      <c r="B3" t="str">
+        <v>mansour 53.185.773</v>
+      </c>
+      <c r="C3" t="str">
+        <v xml:space="preserve">câblage hors armoire sur site </v>
+      </c>
+      <c r="D3">
+        <v>6000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>